--- a/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2830 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10.08.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gillett J.
+ (Aus)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Wembley Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>90 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>78 146</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Winner
+Manchester City</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>guardiola pep</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>ten hag erik</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>482</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>8UHsapgU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>21 401</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>bulut erol</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>le bris regis</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2meCcXHP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21 011</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>walter tim</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>manning liam</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>bJtrhBum</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>36 432</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>farke daniel</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>mousinho john</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CrrhJmvn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26 610</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>ILdqjkAa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16 456</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Qo0ilTvC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kassam Stadium
+ (Oxford)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11 333</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>n1l0n79O</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>corberan carlos</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xQT96Aft</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>25 037</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>schumacher steven</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>04EZ06OH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>17 975</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pCQRkLbJ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>09.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17 948</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>lowe ryan</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>485</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,6324 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AV28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>vDEpovX1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>42DzSumJ</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hanworth</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fBo5RVhP</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Walton &amp; Hersham</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>48</v>
+      </c>
+      <c r="N2" t="n">
+        <v>483</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hxlYyYo4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>23 083</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Newcastle
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>48</v>
+      </c>
+      <c r="N3" t="n">
+        <v>484</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>espirito santo</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>howe eddie</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U32wGjPp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The Cherry Red Records Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9 215</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7 934</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4KREuF43</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>484</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>jackson johnnie</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>mckenna kieran</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hGzqjO6E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7 225</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Southampton
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>48</v>
+      </c>
+      <c r="N5" t="n">
+        <v>484</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>bulut erol</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>martin russell</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OrHrRGXo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Howard P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Colchester Community Stadium
+ (Colchester)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10 105</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6 716</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Brentford
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>484</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>cowley danny</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>frank thomas</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WQF2UUMt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Toner B.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Swansea.com Stadium
+ (Swansea)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21 088</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>hl2V5JIl</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Wycombe
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>484</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>65pf39vc</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>bloomfield matt</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>rkazN4LU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bankes P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>London Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>62 500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>47 381</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+West Ham</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>48</v>
+      </c>
+      <c r="N8" t="n">
+        <v>484</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>lopetegui julen</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>iraola andoni</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GEugARyP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>28.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Molineux Stadium
+ (Wolverhampton)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>31 750</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>19 236</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Wolves</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>48</v>
+      </c>
+      <c r="N9" t="n">
+        <v>484</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>o neil gary</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>parker scott</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Wn71woN8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Stroud K.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>St. Andrew's Stadium
+ (Birmingham)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29 409</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11 949</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SWk4muv7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Fulham
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>48</v>
+      </c>
+      <c r="N10" t="n">
+        <v>484</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>davies chris</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>silva marco</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EkqxE9x0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Selhurst Park
+ (London)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>25 486</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>12 503</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Crystal Palace</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>48</v>
+      </c>
+      <c r="N11" t="n">
+        <v>484</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>glasner oliver</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dUjtW2Fr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Reeves T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Oakwell
+ (Barnsley)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23 287</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10 739</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNGEKMx6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Barnsley</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>48</v>
+      </c>
+      <c r="N12" t="n">
+        <v>484</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>bNLzN2wB</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>clarke darrell</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MFnpCm7C</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stockbridge S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Holker Street
+ (Barrow in Furness)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6 500</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3 003</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Barrow</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>48</v>
+      </c>
+      <c r="N13" t="n">
+        <v>484</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>joDBK9gn</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>clemence stephen</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>UsklUtpe</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9 418</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8EFIJthC</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Blackpool
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>48</v>
+      </c>
+      <c r="N14" t="n">
+        <v>484</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>2e9kg9n1</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>keogh richard</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ddFjPf2b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chilowicz A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Amex Stadium
+ (Brighton)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>31 876</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>19 175</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Brighton</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Crawley</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>48</v>
+      </c>
+      <c r="N15" t="n">
+        <v>484</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>hurzeler fabian</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>lindsey scott</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Sh9BS8ig</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Finnie W.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Coventry Building Society Arena
+ (Coventry)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>32 753</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>11 808</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Coventry</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>48</v>
+      </c>
+      <c r="N16" t="n">
+        <v>484</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dAfPwfHi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Goodison Park
+ (Liverpool)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>39 572</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>37 245</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Everton</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>hlzYDy5q</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Doncaster</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>48</v>
+      </c>
+      <c r="N17" t="n">
+        <v>484</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>dyche sean</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>pSZhI8SM</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>mccann grant</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWQ6LC1N</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Joyce R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Highbury Stadium
+ (Fleetwood)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5 327</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1 744</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Fleetwood</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>KMfM7P4b</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Rotherham</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>48</v>
+      </c>
+      <c r="N18" t="n">
+        <v>484</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>adam charles</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>evans steve</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jiUEFsV1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Corlett M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Blundell Park
+ (Cleethorpes)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9 052</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6 364</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OEaiS3za</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Sheffield Wed
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>48</v>
+      </c>
+      <c r="N19" t="n">
+        <v>484</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>SGvTSGmc</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>artell david</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>rohl danny</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dY0SOQjI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Speedie B.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EnviroVent Stadium
+ (Harrogate)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2 570</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CQv5qrFt</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Harrogate</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Preston
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>48</v>
+      </c>
+      <c r="N20" t="n">
+        <v>484</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>ANwVL1Tp</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>weaver simon</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>heckingbottom paul</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>hO8aNYWA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Smith L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>King Power Stadium
+ (Leicester)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>32 261</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>13 011</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Leicester</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>jVhkb1QE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Tranmere</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>48</v>
+      </c>
+      <c r="N21" t="n">
+        <v>484</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>cooper steven</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2L1wFbM5</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>adkins nigel</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vDA9yPiL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Rock D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5 875</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Leyton Orient
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>48</v>
+      </c>
+      <c r="N22" t="n">
+        <v>484</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>C6Wq1Q6e</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>wellens richie</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hzeTFV7m</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>7 132</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+QPR</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>48</v>
+      </c>
+      <c r="N23" t="n">
+        <v>484</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Q9rcSKE7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gill S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>The Croud Meadow
+ (Shrewsbury)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9 877</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3 220</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>EqfQ6qK4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Shrewsbury</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bolton
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>48</v>
+      </c>
+      <c r="N24" t="n">
+        <v>484</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>EqN1jJFK</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>hurst paul</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>EosAlOi5</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>evatt ian</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>zJCJQnM5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Duckworth E.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bescot Stadium
+ (Walsall)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11 300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3 378</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>YgrfcLuL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Walsall</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Huddersfield</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>484</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>YTxm48Ng</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>sadler mathew john</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>KGX2o9A5</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>duff michael</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>QkntzCGG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vicarage Road
+ (Watford)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>22 200</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8 319</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Watford</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>48</v>
+      </c>
+      <c r="N26" t="n">
+        <v>484</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>rooney wayne</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>rRQ6H30k</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:15</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Eltringham G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>17 408</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Stoke
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>48</v>
+      </c>
+      <c r="N27" t="n">
+        <v>484</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>schumacher steven</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YqcO2yDl</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Madley R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>48</v>
+      </c>
+      <c r="N28" t="n">
+        <v>485</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,5284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jones R.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vitality Stadium
+ (Bournemouth)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>11 307</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>iraola andoni</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>arteta mikel</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>England D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26 600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>26 743</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>silva marco</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>emery unai</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Oliver M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Portman Road
+ (Ipswich)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>29 673</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>29 862</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ipswich</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>mckenna kieran</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>dyche sean</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Barrott S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Old Trafford
+ (Manchester)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>75 635</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>73 738</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Manchester Utd</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>ten hag erik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>frank thomas</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bankes P.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>St. James' Park
+ (Newcastle)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>52 305</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>52 220</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>howe eddie</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>hurzeler fabian</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Taylor A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>St. Mary's Stadium
+ (Southampton)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>32 384</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31 145</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>martin russell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>cooper steven</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Madley A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur Stadium
+ (London)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>62 850</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61 381</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>West Ham</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>postecoglou ange</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>lopetegui julen</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>481</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EJfDwuEj</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EDRBCKEI</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Boston Utd</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>r9s6zO6P</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Gainsborough
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>p44sq1jT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6kTu5zUd</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Brackley Town</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Q1YuCFZe</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Hartlepool</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8EJl8jJs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gateshead International Stadium
+ (Gateshead)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11 800</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>d2vIdDRk</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Gateshead</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>tIEEKOJK</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Hednesford
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dtgtsEKr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>York Road
+ (Maidenhead)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CK7k1GpJ</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Maidenhead</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>GEL99JRB</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Taunton</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2uy8aMzA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fRf75xoR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Peterborough Sports</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4nSNzjG6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Rushall
+Winner</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>fFXa1r6c</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Damson Park
+ (Solihull)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5 500</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>xAcLgIDU</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Solihull Moors</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>v9CGIu4N</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>483</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hSxF3TVr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13 550</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="BA15" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0QDzm8zG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24 438</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>manning liam</t>
+        </is>
+      </c>
+      <c r="BA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6Pu8UaKl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>17 321</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="BA17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jD19YTxK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Linington J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>17 438</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>mousinho john</t>
+        </is>
+      </c>
+      <c r="BA18" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nqmuT70s</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Salisbury M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>28 105</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sheffield Wed</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>rohl danny</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>parker scott</t>
+        </is>
+      </c>
+      <c r="BA19" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rBtlRoVg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>23 002</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>KOLbZJEd</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>pelach narcis</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="BA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CUhG170e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kitchen A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>20 634</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>dIE1p27R</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>riza omer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>fqoqa1yn</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>shuttleworth pete</t>
+        </is>
+      </c>
+      <c r="BA21" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>fDrzkU53</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Martin S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="BA22" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SvUGSwk1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Doughty L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kassam Stadium
+ (Oxford)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>11 453</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>corberan carlos</t>
+        </is>
+      </c>
+      <c r="BA23" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>z5XOQHJD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Smith J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>15 907</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>heckingbottom paul</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="BA24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2JelRQDd</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>18.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Smith L.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>36 695</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>farke daniel</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="BA25" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>485</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,3185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BB14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>KMCY9qSa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>21.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Robinson T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>City Ground
+ (Nottingham)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30 404</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29 443</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Nottingham</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>MeAQUqrN</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>silva rui pedro</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>glasner oliver</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Aau4hOTh</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>23.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Davies A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Riverside Stadium
+ (Middlesbrough)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>34 742</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24 303</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6F0lvLNC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>MeKPSerA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sheffield Utd</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>carrick michael</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>wilder chris</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bLBozsEO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Busby J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ewood Park
+ (Blackburn)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31 367</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13 647</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>eustace john</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>corberan carlos</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jypdPPa6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Whitestone D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MKM Stadium
+ (Hull)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25 586</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20 168</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>S66R0t75</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hull</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>walter tim</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>parker scott</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2Zydfpat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nield T.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kenilworth Road
+ (Luton)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12 300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11 332</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>MBpIn2MH</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>edwards rob</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>le bris regis</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RYCj2b5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Allison S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The Den
+ (London)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 146</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13 954</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>WpGM6ELj</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Plymouth</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>harris neil</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>WfXv1DCa</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>rooney wayne</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Ao0VwPEa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bell J.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Loftus Road
+ (London)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18 439</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14 173</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>lrMHUHDc</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Coventry</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>cifuentes marti</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lYgfxNV9</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>robins mark</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KfdOaoV7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Langford O.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cardiff City Stadium
+ (Cardiff)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>33 280</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>18 534</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>zckREQFJ</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>dIE1p27R</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>riza omer</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>djl0V3o6</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>mousinho john</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CjY4N3UI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Backhouse A.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Elland Road
+ (Leeds)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>37 792</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>34 968</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>UmMRoGzp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>farke daniel</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>cleverley tom</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ImLjo7MP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ward G.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kassam Stadium
+ (Oxford)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11 423</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>vgOBT43c</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Oxford Utd</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Iug0YO0Q</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>buckingham des</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>warne paul</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>xY1Nuopm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Finnie W.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Deepdale
+ (Preston)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>23 408</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>13 677</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x8IDVcbi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Preston</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Norwich</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>lGE8iEO1</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>heckingbottom paul</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>thorup johannes</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0jZANlNE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Donohue M.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hillsborough
+ (Sheffield)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>39 732</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>22 452</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>llcCvIcG</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sheffield Wed</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>rohl danny</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>williams luke</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6Dgvx3qC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Webb D.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bet365 Stadium
+ (Stoke on Trent)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30 089</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>19 679</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Stoke</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>KOLbZJEd</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>pelach narcis</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>manning liam</t>
+        </is>
+      </c>
+      <c r="AY14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>485</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/england/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,657 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>04.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Attwell S.
+ (Eng)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Craven Cottage
+ (London)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29 589</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24 931</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>silva marco</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>frank thomas</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>481</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>vwSGH1jf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04.11.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>The Meadow
+ (Chesham)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3 963</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>K8DIJrZQ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Chesham</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>hrHTRs5B</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Lincoln
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>483</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>